--- a/DAY-8/Browser.xlsx
+++ b/DAY-8/Browser.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanam\Documents\UiPath\DAY-8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE219D2-F213-4356-9393-34667F3020E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6DD58C-E7A4-44F5-9566-3C47E5DA8314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="2820" windowWidth="17280" windowHeight="8880" xr2:uid="{D6C621E3-86E9-403F-B764-DDD5154B047F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D6C621E3-86E9-403F-B764-DDD5154B047F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -426,10 +426,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1">
-        <v>0.55000000000000004</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -437,10 +437,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -448,10 +448,10 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
